--- a/data/trans_orig/P1427-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1427-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cataratas en 2012</t>
+          <t>Población con diagnóstico de cataratas en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17917</t>
+          <t>17949</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>5515</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18314</t>
+          <t>18852</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>13421</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30232</t>
+          <t>32329</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276821</t>
+          <t>276789</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289328</t>
+          <t>289666</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268931</t>
+          <t>268393</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>281754</t>
+          <t>281730</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>551751</t>
+          <t>549654</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>568781</t>
+          <t>568562</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11472</t>
+          <t>12109</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30564</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>494055</t>
+          <t>493418</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503542</t>
+          <t>503523</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>497539</t>
+          <t>499086</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>516236</t>
+          <t>516324</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>998839</t>
+          <t>998728</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1017726</t>
+          <t>1017779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>10931</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2148</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13166</t>
+          <t>12795</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19258</t>
+          <t>19530</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312477</t>
+          <t>313115</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322113</t>
+          <t>322106</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327854</t>
+          <t>328225</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>338898</t>
+          <t>338872</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>645808</t>
+          <t>645536</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>659121</t>
+          <t>658969</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18598</t>
+          <t>15808</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23228</t>
+          <t>21385</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13385</t>
+          <t>13237</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32108</t>
+          <t>31725</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>355384</t>
+          <t>358174</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>369700</t>
+          <t>369980</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>365723</t>
+          <t>367566</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>381674</t>
+          <t>381825</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>730825</t>
+          <t>731208</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>749548</t>
+          <t>749696</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17354</t>
+          <t>17980</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20247</t>
+          <t>20783</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14236</t>
+          <t>14425</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32503</t>
+          <t>33444</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195264</t>
+          <t>194638</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207471</t>
+          <t>208202</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199344</t>
+          <t>198808</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>213303</t>
+          <t>213471</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>399706</t>
+          <t>398765</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>417973</t>
+          <t>417784</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>7096</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9828</t>
+          <t>9946</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13192</t>
+          <t>12122</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>267439</t>
+          <t>266885</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>268268</t>
+          <t>268150</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277091</t>
+          <t>277080</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>538885</t>
+          <t>539955</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>549900</t>
+          <t>549948</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7327</t>
+          <t>8025</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25256</t>
+          <t>25762</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8465</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25472</t>
+          <t>26064</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19259</t>
+          <t>19446</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44183</t>
+          <t>43035</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>637532</t>
+          <t>637026</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>655461</t>
+          <t>654763</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>668381</t>
+          <t>667789</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>685388</t>
+          <t>685290</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1312458</t>
+          <t>1313606</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1337382</t>
+          <t>1337195</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25907</t>
+          <t>24732</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10983</t>
+          <t>10881</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28350</t>
+          <t>29297</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22011</t>
+          <t>21363</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>47941</t>
+          <t>47610</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>753191</t>
+          <t>754366</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>772559</t>
+          <t>772652</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>794228</t>
+          <t>793281</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>811595</t>
+          <t>811697</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1553735</t>
+          <t>1554066</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1579665</t>
+          <t>1580313</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>52410</t>
+          <t>53484</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>87241</t>
+          <t>86156</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>75468</t>
+          <t>75593</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>116097</t>
+          <t>116739</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>135571</t>
+          <t>136186</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>188428</t>
+          <t>188561</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3339538</t>
+          <t>3340623</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3374369</t>
+          <t>3373295</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3439001</t>
+          <t>3438359</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3479630</t>
+          <t>3479505</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6793449</t>
+          <t>6793316</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6846306</t>
+          <t>6845691</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cataratas en 2016</t>
+          <t>Población con diagnóstico de cataratas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>922</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7948</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17401</t>
+          <t>18730</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21409</t>
+          <t>22629</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>285813</t>
+          <t>285719</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293761</t>
+          <t>292839</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271302</t>
+          <t>269973</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284151</t>
+          <t>284252</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>561055</t>
+          <t>559835</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575502</t>
+          <t>575658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12811</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14770</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>497743</t>
+          <t>496668</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>510273</t>
+          <t>509963</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1010889</t>
+          <t>1010953</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1022516</t>
+          <t>1022860</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>10880</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11393</t>
+          <t>12008</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17487</t>
+          <t>18684</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307976</t>
+          <t>307685</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316690</t>
+          <t>316671</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>324916</t>
+          <t>324301</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334335</t>
+          <t>334262</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>637387</t>
+          <t>636190</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>649345</t>
+          <t>649117</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>828</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8115</t>
+          <t>7664</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13806</t>
+          <t>13574</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17470</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>361849</t>
+          <t>362300</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>369144</t>
+          <t>369136</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>373477</t>
+          <t>373709</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>384940</t>
+          <t>385049</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>739777</t>
+          <t>739566</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>753245</t>
+          <t>752564</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13814</t>
+          <t>14336</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13583</t>
+          <t>13390</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>209318</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211221</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204773</t>
+          <t>204251</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216380</t>
+          <t>216152</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>416225</t>
+          <t>416418</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>427415</t>
+          <t>427462</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10041</t>
+          <t>10062</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16636</t>
+          <t>15326</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21709</t>
+          <t>21737</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253082</t>
+          <t>253061</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261491</t>
+          <t>261537</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>256479</t>
+          <t>257789</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>269521</t>
+          <t>269554</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>514529</t>
+          <t>514501</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>529023</t>
+          <t>529312</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18649</t>
+          <t>19602</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>11378</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31058</t>
+          <t>30163</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20528</t>
+          <t>20654</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42878</t>
+          <t>43113</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>637909</t>
+          <t>636956</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>650745</t>
+          <t>650957</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>660236</t>
+          <t>661131</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>679383</t>
+          <t>679916</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1304974</t>
+          <t>1304739</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1327324</t>
+          <t>1327198</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14367</t>
+          <t>14937</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>11524</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28837</t>
+          <t>32125</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>17646</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38255</t>
+          <t>39547</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>764216</t>
+          <t>763646</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775226</t>
+          <t>775132</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>797330</t>
+          <t>794042</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>815410</t>
+          <t>814643</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1566495</t>
+          <t>1565203</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1587598</t>
+          <t>1587104</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25491</t>
+          <t>25073</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48148</t>
+          <t>48345</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>61224</t>
+          <t>63420</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>100147</t>
+          <t>99565</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>93749</t>
+          <t>93876</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>137383</t>
+          <t>139477</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3346202</t>
+          <t>3346005</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3368859</t>
+          <t>3369277</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3444395</t>
+          <t>3444977</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3483318</t>
+          <t>3481122</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6801509</t>
+          <t>6799415</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6845143</t>
+          <t>6845016</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7183,7 +7183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cataratas en 2023</t>
+          <t>Población con diagnóstico de cataratas en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1692</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>307403</t>
+          <t>307438</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283765</t>
+          <t>283776</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>288472</t>
+          <t>288526</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>593992</t>
+          <t>594270</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>599385</t>
+          <t>599555</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>5794</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18650</t>
+          <t>18752</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28973</t>
+          <t>28444</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23197</t>
+          <t>22811</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42425</t>
+          <t>42275</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496520</t>
+          <t>496418</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>509066</t>
+          <t>509376</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>485318</t>
+          <t>485847</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>499610</t>
+          <t>500283</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>987036</t>
+          <t>987186</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1006264</t>
+          <t>1006650</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13233</t>
+          <t>12893</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26711</t>
+          <t>25515</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,47 +8079,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>20505</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>14629</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>27208</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5,87%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>4,19%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>20505</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>14980</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>27795</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,87%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30557</t>
+          <t>31539</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>49260</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>289339</t>
+          <t>290535</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>302817</t>
+          <t>303157</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,49 +8192,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>95,92%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>328623</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>321920</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>334499</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>94,13%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>92,21%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>95,81%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>494</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>328623</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>321333</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>334148</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,13%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>92,04%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>95,71%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>823</t>
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>615589</t>
+          <t>615918</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>634621</t>
+          <t>633639</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3571</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>12305</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13940</t>
+          <t>13929</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>9875</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22341</t>
+          <t>22693</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>300509</t>
+          <t>300252</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>309397</t>
+          <t>308986</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>461147</t>
+          <t>461158</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>470141</t>
+          <t>470537</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>765303</t>
+          <t>764951</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>777719</t>
+          <t>777769</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13582</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11487</t>
+          <t>11570</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11383</t>
+          <t>11468</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21939</t>
+          <t>21795</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>165160</t>
+          <t>165293</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>173881</t>
+          <t>173551</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196787</t>
+          <t>196704</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203250</t>
+          <t>203321</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>365077</t>
+          <t>365221</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>375633</t>
+          <t>375548</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22705</t>
+          <t>22500</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36684</t>
+          <t>37806</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>24778</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37987</t>
+          <t>37525</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50719</t>
+          <t>51034</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70182</t>
+          <t>70492</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>232952</t>
+          <t>231830</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>246931</t>
+          <t>247136</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>217966</t>
+          <t>218428</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>231708</t>
+          <t>231175</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>455407</t>
+          <t>455097</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>474870</t>
+          <t>474555</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13363</t>
+          <t>13276</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31876</t>
+          <t>30890</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17509</t>
+          <t>20222</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59718</t>
+          <t>61039</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39855</t>
+          <t>40571</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79989</t>
+          <t>80523</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>590982</t>
+          <t>591968</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>609495</t>
+          <t>609582</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>788900</t>
+          <t>787579</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>831109</t>
+          <t>828396</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1391487</t>
+          <t>1390953</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1431621</t>
+          <t>1430905</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3446</t>
+          <t>3492</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16743</t>
+          <t>17015</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15537</t>
+          <t>15450</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43561</t>
+          <t>42486</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19455</t>
+          <t>20745</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52676</t>
+          <t>53219</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>911977</t>
+          <t>911705</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>925274</t>
+          <t>925228</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>671831</t>
+          <t>672906</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>699855</t>
+          <t>699942</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1591436</t>
+          <t>1590893</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1624657</t>
+          <t>1623367</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>82159</t>
+          <t>80934</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>125938</t>
+          <t>125683</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>126816</t>
+          <t>124658</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>181219</t>
+          <t>181666</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>228171</t>
+          <t>226231</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>296101</t>
+          <t>294663</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3329238</t>
+          <t>3329493</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3373017</t>
+          <t>3374242</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10255,7 +10255,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3475158</t>
+          <t>3474711</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3529561</t>
+          <t>3531719</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6815452</t>
+          <t>6816890</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6883382</t>
+          <t>6885322</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1427-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1427-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17949</t>
+          <t>17567</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18852</t>
+          <t>18971</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13421</t>
+          <t>13294</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32329</t>
+          <t>31730</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276789</t>
+          <t>277171</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289666</t>
+          <t>289742</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268393</t>
+          <t>268274</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>281730</t>
+          <t>281917</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>549654</t>
+          <t>550253</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>568562</t>
+          <t>568689</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12109</t>
+          <t>11415</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7441</t>
+          <t>7775</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>25139</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30564</t>
+          <t>30191</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>493418</t>
+          <t>494112</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503523</t>
+          <t>503543</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>499086</t>
+          <t>498626</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>516324</t>
+          <t>515990</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>998728</t>
+          <t>999101</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1017779</t>
+          <t>1017674</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10931</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12795</t>
+          <t>12937</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19530</t>
+          <t>19416</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313115</t>
+          <t>313005</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322106</t>
+          <t>322096</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>328225</t>
+          <t>328083</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>338872</t>
+          <t>338039</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>645536</t>
+          <t>645650</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15808</t>
+          <t>15871</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7126</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21385</t>
+          <t>22261</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13237</t>
+          <t>14002</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31725</t>
+          <t>32713</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>358174</t>
+          <t>358111</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>369980</t>
+          <t>369815</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>367566</t>
+          <t>366690</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>381825</t>
+          <t>381845</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>731208</t>
+          <t>730220</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>749696</t>
+          <t>748931</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17980</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20783</t>
+          <t>20281</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14425</t>
+          <t>13619</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33444</t>
+          <t>31689</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194638</t>
+          <t>194849</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208202</t>
+          <t>207484</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>198808</t>
+          <t>199310</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>213471</t>
+          <t>213803</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>398765</t>
+          <t>400520</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>417784</t>
+          <t>418590</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>7552</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>986</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>9018</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12122</t>
+          <t>12324</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>266885</t>
+          <t>266429</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>268150</t>
+          <t>269078</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277080</t>
+          <t>277110</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>539955</t>
+          <t>539753</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>549948</t>
+          <t>549992</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8025</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25762</t>
+          <t>25121</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,44 +2805,44 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>15472</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>8417</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>26071</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>1,21%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>15472</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>8563</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>26064</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
           <t>3,76%</t>
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19446</t>
+          <t>19063</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43035</t>
+          <t>41689</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>637026</t>
+          <t>637667</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>654763</t>
+          <t>655583</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,49 +2918,49 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>678381</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>667782</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>685436</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>96,24%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
           <t>98,79%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>678381</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>667789</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>685290</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>97,77%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>96,24%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1228</t>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1313606</t>
+          <t>1314952</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1337195</t>
+          <t>1337578</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24732</t>
+          <t>23779</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10801</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29297</t>
+          <t>28823</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21363</t>
+          <t>21686</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>47610</t>
+          <t>47774</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>754366</t>
+          <t>755319</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>772652</t>
+          <t>772444</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>793281</t>
+          <t>793755</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>811697</t>
+          <t>811777</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1554066</t>
+          <t>1553902</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1580313</t>
+          <t>1579990</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>53484</t>
+          <t>52928</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>86156</t>
+          <t>88371</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>75593</t>
+          <t>76098</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>116739</t>
+          <t>117673</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>136186</t>
+          <t>136074</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>188561</t>
+          <t>187911</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3340623</t>
+          <t>3338408</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3373295</t>
+          <t>3373851</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3438359</t>
+          <t>3437425</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3479505</t>
+          <t>3479000</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6793316</t>
+          <t>6793966</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6845691</t>
+          <t>6845803</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>919</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>4349</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18730</t>
+          <t>18136</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6806</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22629</t>
+          <t>21384</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>285719</t>
+          <t>285610</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292839</t>
+          <t>292842</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269973</t>
+          <t>270567</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284252</t>
+          <t>284354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>559835</t>
+          <t>561080</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575658</t>
+          <t>576288</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>12744</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>14885</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496668</t>
+          <t>497207</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>509963</t>
+          <t>510340</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>520820</t>
+          <t>520754</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1010953</t>
+          <t>1010774</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1022860</t>
+          <t>1022491</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10880</t>
+          <t>11032</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12008</t>
+          <t>11547</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18684</t>
+          <t>17680</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307685</t>
+          <t>307533</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316671</t>
+          <t>316813</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>324301</t>
+          <t>324762</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334262</t>
+          <t>334441</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>636190</t>
+          <t>637194</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>649117</t>
+          <t>649446</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>831</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7664</t>
+          <t>7815</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13574</t>
+          <t>13051</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17681</t>
+          <t>17796</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>362300</t>
+          <t>362149</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>369136</t>
+          <t>369133</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>373709</t>
+          <t>374232</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>385049</t>
+          <t>385062</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>739566</t>
+          <t>739451</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>752564</t>
+          <t>752541</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14336</t>
+          <t>13676</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13390</t>
+          <t>13705</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204251</t>
+          <t>204911</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216152</t>
+          <t>216210</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>416418</t>
+          <t>416103</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>427462</t>
+          <t>427471</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10062</t>
+          <t>9048</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15326</t>
+          <t>15177</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,47 +5820,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>5,56%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>12514</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>6961</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>22537</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>1,3%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>12514</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>6926</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>21737</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253061</t>
+          <t>254075</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261537</t>
+          <t>261530</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>257789</t>
+          <t>257938</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>269554</t>
+          <t>269416</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,47 +5933,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>523724</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>513701</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>529277</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>97,67%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>95,8%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>98,7%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>523724</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>514501</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>529312</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>97,67%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>95,95%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19602</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11378</t>
+          <t>11241</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30163</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20654</t>
+          <t>21518</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43113</t>
+          <t>44513</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>636956</t>
+          <t>637328</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>650957</t>
+          <t>650303</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>661131</t>
+          <t>660646</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>679916</t>
+          <t>680053</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1304739</t>
+          <t>1303339</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1327198</t>
+          <t>1326334</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14937</t>
+          <t>15645</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11524</t>
+          <t>11716</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32125</t>
+          <t>30476</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17646</t>
+          <t>17920</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39547</t>
+          <t>39503</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>763646</t>
+          <t>762938</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775132</t>
+          <t>775311</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>794042</t>
+          <t>795691</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>814643</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1565203</t>
+          <t>1565247</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1587104</t>
+          <t>1586830</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25073</t>
+          <t>25492</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48345</t>
+          <t>48016</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>63420</t>
+          <t>63030</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>99565</t>
+          <t>100160</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>93876</t>
+          <t>96676</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>139477</t>
+          <t>141206</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3346005</t>
+          <t>3346334</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3369277</t>
+          <t>3368858</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3444977</t>
+          <t>3444382</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3481122</t>
+          <t>3481512</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6799415</t>
+          <t>6797686</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6845016</t>
+          <t>6842216</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7408,32 +7408,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7443,32 +7443,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -7486,27 +7486,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>310518</t>
+          <t>317442</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>307438</t>
+          <t>314043</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7521,32 +7521,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>286886</t>
+          <t>312615</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283776</t>
+          <t>309421</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>288526</t>
+          <t>314609</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7556,32 +7556,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>597404</t>
+          <t>630057</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>594270</t>
+          <t>625078</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>599555</t>
+          <t>632455</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -7599,17 +7599,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7634,17 +7634,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7669,17 +7669,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7716,32 +7716,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11184</t>
+          <t>11635</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18752</t>
+          <t>20334</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7751,32 +7751,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20445</t>
+          <t>22163</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14008</t>
+          <t>15485</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28444</t>
+          <t>30563</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7786,32 +7786,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>31629</t>
+          <t>33798</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22811</t>
+          <t>24854</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42275</t>
+          <t>45651</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -7829,32 +7829,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>503986</t>
+          <t>515728</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496418</t>
+          <t>507029</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>509376</t>
+          <t>520805</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7864,32 +7864,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>493846</t>
+          <t>523646</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>485847</t>
+          <t>515246</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500283</t>
+          <t>530324</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7899,32 +7899,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>997832</t>
+          <t>1039374</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>987186</t>
+          <t>1027521</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1006650</t>
+          <t>1048318</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -7942,17 +7942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>515170</t>
+          <t>527363</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>515170</t>
+          <t>527363</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>515170</t>
+          <t>527363</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7977,17 +7977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8012,17 +8012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1029461</t>
+          <t>1073172</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1029461</t>
+          <t>1073172</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1029461</t>
+          <t>1073172</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8059,32 +8059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19083</t>
+          <t>18732</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25515</t>
+          <t>27127</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8094,32 +8094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20505</t>
+          <t>20642</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>14502</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27208</t>
+          <t>27704</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8129,32 +8129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>39588</t>
+          <t>39374</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31539</t>
+          <t>31442</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49260</t>
+          <t>49263</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -8172,32 +8172,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>296967</t>
+          <t>297261</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>290535</t>
+          <t>288866</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>303157</t>
+          <t>302671</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8207,32 +8207,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>328623</t>
+          <t>335739</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>321920</t>
+          <t>328677</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334499</t>
+          <t>341879</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8242,32 +8242,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>625590</t>
+          <t>633001</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>615918</t>
+          <t>623112</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>633639</t>
+          <t>640933</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -8285,17 +8285,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8355,17 +8355,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8402,32 +8402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12305</t>
+          <t>12825</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8437,32 +8437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8794</t>
+          <t>9253</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13929</t>
+          <t>13435</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8472,32 +8472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>15477</t>
+          <t>16213</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>10945</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22693</t>
+          <t>23380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -8515,32 +8515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>305874</t>
+          <t>366184</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>300252</t>
+          <t>360320</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>308986</t>
+          <t>369514</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8550,32 +8550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>466293</t>
+          <t>412019</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>461158</t>
+          <t>407837</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>470537</t>
+          <t>415629</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8585,32 +8585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>772167</t>
+          <t>778204</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>764951</t>
+          <t>771037</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>777769</t>
+          <t>783472</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -8628,17 +8628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475087</t>
+          <t>421272</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475087</t>
+          <t>421272</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475087</t>
+          <t>421272</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8698,17 +8698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787644</t>
+          <t>794417</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787644</t>
+          <t>794417</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787644</t>
+          <t>794417</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8745,32 +8745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8278</t>
+          <t>8691</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13449</t>
+          <t>13340</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8780,32 +8780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>8037</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11570</t>
+          <t>11774</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8815,32 +8815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>16031</t>
+          <t>16728</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11468</t>
+          <t>11971</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21795</t>
+          <t>22907</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -8858,32 +8858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>170464</t>
+          <t>196974</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>165293</t>
+          <t>192325</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>173551</t>
+          <t>200607</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8893,32 +8893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>200521</t>
+          <t>218786</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196704</t>
+          <t>215049</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203321</t>
+          <t>221908</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8928,32 +8928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>370985</t>
+          <t>415760</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>365221</t>
+          <t>409581</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>375548</t>
+          <t>420517</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -8971,17 +8971,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9006,17 +9006,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9088,32 +9088,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29082</t>
+          <t>28917</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22500</t>
+          <t>22508</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37806</t>
+          <t>37161</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9123,32 +9123,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31020</t>
+          <t>31491</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24778</t>
+          <t>25521</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37525</t>
+          <t>39055</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9158,32 +9158,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>60103</t>
+          <t>60408</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51034</t>
+          <t>50399</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70492</t>
+          <t>70302</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -9201,32 +9201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>240554</t>
+          <t>241790</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231830</t>
+          <t>233546</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>247136</t>
+          <t>248199</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9236,32 +9236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>224933</t>
+          <t>231151</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>218428</t>
+          <t>223587</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>231175</t>
+          <t>237121</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9271,32 +9271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>465486</t>
+          <t>472941</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>455097</t>
+          <t>463047</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>474555</t>
+          <t>482950</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>
@@ -9314,17 +9314,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9349,17 +9349,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>255953</t>
+          <t>262642</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>255953</t>
+          <t>262642</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>255953</t>
+          <t>262642</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>525589</t>
+          <t>533349</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>525589</t>
+          <t>533349</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>525589</t>
+          <t>533349</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9431,32 +9431,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>22657</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13276</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30890</t>
+          <t>34587</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9466,32 +9466,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>42276</t>
+          <t>49548</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20222</t>
+          <t>40295</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61039</t>
+          <t>64348</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9501,32 +9501,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>62855</t>
+          <t>72205</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40571</t>
+          <t>58681</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80523</t>
+          <t>88295</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -9544,32 +9544,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>602279</t>
+          <t>695294</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>591968</t>
+          <t>683364</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>609582</t>
+          <t>702834</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9579,32 +9579,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>806342</t>
+          <t>721785</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>787579</t>
+          <t>706985</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>828396</t>
+          <t>731038</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9614,32 +9614,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1408621</t>
+          <t>1417079</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1390953</t>
+          <t>1400989</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1430905</t>
+          <t>1430603</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -9657,17 +9657,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>622858</t>
+          <t>717951</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>622858</t>
+          <t>717951</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>622858</t>
+          <t>717951</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9692,17 +9692,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848618</t>
+          <t>771333</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848618</t>
+          <t>771333</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848618</t>
+          <t>771333</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9727,17 +9727,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1471476</t>
+          <t>1489284</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1471476</t>
+          <t>1489284</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1471476</t>
+          <t>1489284</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9774,32 +9774,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>9631</t>
+          <t>10623</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17015</t>
+          <t>17312</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9809,32 +9809,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>23250</t>
+          <t>20847</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15450</t>
+          <t>14474</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42486</t>
+          <t>28940</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9844,32 +9844,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>32881</t>
+          <t>31470</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20745</t>
+          <t>23529</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>53219</t>
+          <t>41576</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -9887,32 +9887,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>919089</t>
+          <t>787449</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>911705</t>
+          <t>780760</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>925228</t>
+          <t>791953</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9922,32 +9922,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>692142</t>
+          <t>809762</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>672906</t>
+          <t>801669</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>699942</t>
+          <t>816135</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9957,32 +9957,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1611231</t>
+          <t>1597211</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1590893</t>
+          <t>1587105</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1623367</t>
+          <t>1605152</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -10000,17 +10000,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10035,17 +10035,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10070,17 +10070,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10117,32 +10117,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>105444</t>
+          <t>109619</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>80934</t>
+          <t>92165</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>125683</t>
+          <t>128153</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10152,32 +10152,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>156792</t>
+          <t>165427</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>124658</t>
+          <t>146671</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>181666</t>
+          <t>186357</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10187,32 +10187,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>262236</t>
+          <t>275046</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>226231</t>
+          <t>250908</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>294663</t>
+          <t>304092</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -10230,32 +10230,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3349732</t>
+          <t>3418123</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3329493</t>
+          <t>3399589</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3374242</t>
+          <t>3435577</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10265,32 +10265,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3499585</t>
+          <t>3565504</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3474711</t>
+          <t>3544574</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3531719</t>
+          <t>3584260</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10300,32 +10300,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6849317</t>
+          <t>6983626</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6816890</t>
+          <t>6954580</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6885322</t>
+          <t>7007764</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -10343,17 +10343,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3455176</t>
+          <t>3527742</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3455176</t>
+          <t>3527742</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3455176</t>
+          <t>3527742</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10378,17 +10378,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3656377</t>
+          <t>3730931</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3656377</t>
+          <t>3730931</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3656377</t>
+          <t>3730931</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10413,17 +10413,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7111553</t>
+          <t>7258672</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7111553</t>
+          <t>7258672</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7111553</t>
+          <t>7258672</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
